--- a/AAII_Financials/Yearly/PARA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PARA_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>PARA</t>
   </si>
@@ -656,148 +656,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>29652000</v>
+      </c>
+      <c r="E8" s="3">
         <v>30154000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28586000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>25285000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>26998000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>26425000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>26535000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13166000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12671000</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>22388000</v>
+      </c>
+      <c r="E9" s="3">
         <v>19845000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>17744000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14833000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16713000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15399000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15483000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7956000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7911000</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7264000</v>
+      </c>
+      <c r="E10" s="3">
         <v>10309000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10842000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10452000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10285000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11026000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11052000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5210000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4760000</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -810,8 +822,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -839,9 +852,12 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,69 +885,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E14" s="3">
         <v>705000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>228000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>928000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>819000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>517000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>711000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>249000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>390000</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>418000</v>
+      </c>
+      <c r="E15" s="3">
         <v>405000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>390000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>405000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>438000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>427000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>443000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>225000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>235000</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,68 +966,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>30074000</v>
+      </c>
+      <c r="E17" s="3">
         <v>27932000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>22417000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21272000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>22852000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21345000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>21232000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10475000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10013000</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-422000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2222000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6169000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4013000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4146000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5080000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5303000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2691000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2658000</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,158 +1047,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-25000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>23000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>165000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>39000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-66000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-95000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-50000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5000</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2602000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6582000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4608000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4628000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5447000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5651000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2866000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2898000</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>920000</v>
+      </c>
+      <c r="E22" s="3">
         <v>931000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>986000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1031000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>962000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1030000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1088000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>411000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>399000</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1253000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1266000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5206000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3147000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3223000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3984000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4120000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2230000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2264000</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-361000</v>
+      </c>
+      <c r="E24" s="3">
         <v>227000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>646000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>535000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>15000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>660000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>796000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>628000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>676000</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,69 +1242,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-892000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1039000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4560000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2612000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3208000</v>
-      </c>
-      <c r="H26" s="3">
-        <v>3324000</v>
       </c>
       <c r="I26" s="3">
         <v>3324000</v>
       </c>
       <c r="J26" s="3">
+        <v>3324000</v>
+      </c>
+      <c r="K26" s="3">
         <v>1602000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1588000</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1342000</v>
+      </c>
+      <c r="E27" s="3">
         <v>667000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4336800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2305000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3124000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3240000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3276000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1552000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1554000</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,39 +1341,45 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>676000</v>
+      </c>
+      <c r="E29" s="3">
         <v>379000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>162000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>117000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>184000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>215000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-955000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-291000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-141000</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,69 +1440,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-89000</v>
+      </c>
+      <c r="E32" s="3">
         <v>25000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-23000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-165000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-39000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>66000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>95000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>50000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5000</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-666000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1046000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4498800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2422000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3308000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3455000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2321000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1261000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1413000</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,74 +1539,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-666000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1046000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4498800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2422000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3308000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3455000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2321000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1261000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1413000</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,38 +1643,42 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2460000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2885000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6267000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2984000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>632000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>856000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>285000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>598000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>323000</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1617,146 +1706,161 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7115000</v>
+      </c>
+      <c r="E43" s="3">
         <v>7412000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6984000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7017000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6837000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7199000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3697000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3314000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3628000</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1414000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1342000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1504000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1757000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2813000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2785000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1828000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1427000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1271000</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1714000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2095000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1921000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2021000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1620000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1067000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>463000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>724000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>525000</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12703000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13734000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16676000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13779000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11902000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11880000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6273000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6063000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5747000</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E47" s="3">
         <v>375000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>627000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>601000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>753000</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
@@ -1767,69 +1871,78 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2849000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3153000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3366000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3596000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3783000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2079000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1280000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1241000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1405000</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19105000</v>
+      </c>
+      <c r="E49" s="3">
         <v>19193000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19356000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19438000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19535000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19469000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7557000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7497000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11995000</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,39 +2003,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18790000</v>
+      </c>
+      <c r="E52" s="3">
         <v>21938000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>18595000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15249000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13612000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11069000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5733000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9437000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4618000</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,39 +2069,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>53543000</v>
+      </c>
+      <c r="E54" s="3">
         <v>58393000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>58620000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>52663000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>49585000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>44497000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20843000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24238000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23765000</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,188 +2135,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1100000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1403000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>800000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>571000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>632000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>502000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>231000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>148000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>192000</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="3">
         <v>239000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>16000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>717000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1687000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>698000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>473000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>222000</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8555000</v>
+      </c>
+      <c r="E59" s="3">
         <v>9549000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8668000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7709000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9199000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7866000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3043000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3087000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3146000</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9656000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11191000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9479000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8296000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9048000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8321000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3972000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3708000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3560000</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14601000</v>
+      </c>
+      <c r="E61" s="3">
         <v>15607000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>17698000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19717000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18002000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18100000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9464000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8902000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8226000</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6228000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7789000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8153000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8177000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8729000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7334000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5387000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5488000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6344000</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,39 +2429,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>31017000</v>
+      </c>
+      <c r="E66" s="3">
         <v>35357000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>36218000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>37292000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36378000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34048000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18865000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20549000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18202000</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,39 +2609,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>13829000</v>
+      </c>
+      <c r="E72" s="3">
         <v>14737000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>14343000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10375000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8494000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5569000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-18900000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-19257000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-20518000</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,39 +2741,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22526000</v>
+      </c>
+      <c r="E76" s="3">
         <v>23036000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22402000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15371000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13207000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10449000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1978000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3689000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5563000</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,74 +2807,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-666000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1046000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4498800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2422000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3308000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3455000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2321000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1261000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1413000</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,38 +2896,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>418000</v>
+      </c>
+      <c r="E83" s="3">
         <v>405000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>390000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>430000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>443000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>433000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>443000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>225000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>235000</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,39 +3091,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>475000</v>
+      </c>
+      <c r="E89" s="3">
         <v>219000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>953000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2294000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1230000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3464000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2439000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1685000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1394000</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,38 +3142,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-328000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-358000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-354000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-324000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-353000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-352000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-356000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-196000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-171000</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,39 +3238,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>942000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-526000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2395000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>56000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-155000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-611000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>126000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-340000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>154000</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,38 +3289,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-447000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-689000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-647000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-600000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-595000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-599000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-616000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-288000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-300000</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,97 +3418,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1841000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2981000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-152000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-90000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1216000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2531000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3009000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1046000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1653000</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-94000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-48000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>25000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-25000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>58000</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-425000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3382000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3148000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2285000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-142000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>297000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-386000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>299000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-105000</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PARA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PARA_YR_FIN.xlsx
@@ -748,7 +748,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>22388000</v>
+        <v>20418000</v>
       </c>
       <c r="E9" s="3">
         <v>19845000</v>
@@ -781,7 +781,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>7264000</v>
+        <v>9234000</v>
       </c>
       <c r="E10" s="3">
         <v>10309000</v>
@@ -895,22 +895,22 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>23000</v>
+        <v>2146000</v>
       </c>
       <c r="E14" s="3">
-        <v>705000</v>
+        <v>770000</v>
       </c>
       <c r="F14" s="3">
-        <v>228000</v>
+        <v>271000</v>
       </c>
       <c r="G14" s="3">
-        <v>928000</v>
+        <v>997000</v>
       </c>
       <c r="H14" s="3">
-        <v>819000</v>
+        <v>918000</v>
       </c>
       <c r="I14" s="3">
-        <v>517000</v>
+        <v>585000</v>
       </c>
       <c r="J14" s="3">
         <v>711000</v>
@@ -973,19 +973,19 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>30074000</v>
+        <v>30227000</v>
       </c>
       <c r="E17" s="3">
-        <v>27932000</v>
+        <v>27997000</v>
       </c>
       <c r="F17" s="3">
-        <v>22417000</v>
+        <v>22460000</v>
       </c>
       <c r="G17" s="3">
-        <v>21272000</v>
+        <v>21341000</v>
       </c>
       <c r="H17" s="3">
-        <v>22852000</v>
+        <v>22951000</v>
       </c>
       <c r="I17" s="3">
         <v>21345000</v>
@@ -1006,19 +1006,19 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-422000</v>
+        <v>-575000</v>
       </c>
       <c r="E18" s="3">
-        <v>2222000</v>
+        <v>2157000</v>
       </c>
       <c r="F18" s="3">
-        <v>6169000</v>
+        <v>6126000</v>
       </c>
       <c r="G18" s="3">
-        <v>4013000</v>
+        <v>3944000</v>
       </c>
       <c r="H18" s="3">
-        <v>4146000</v>
+        <v>4047000</v>
       </c>
       <c r="I18" s="3">
         <v>5080000</v>
@@ -1054,19 +1054,19 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>89000</v>
+        <v>242000</v>
       </c>
       <c r="E20" s="3">
-        <v>-25000</v>
+        <v>40000</v>
       </c>
       <c r="F20" s="3">
-        <v>23000</v>
+        <v>66000</v>
       </c>
       <c r="G20" s="3">
-        <v>165000</v>
+        <v>234000</v>
       </c>
       <c r="H20" s="3">
-        <v>39000</v>
+        <v>138000</v>
       </c>
       <c r="I20" s="3">
         <v>-66000</v>
@@ -1450,19 +1450,19 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-89000</v>
+        <v>-242000</v>
       </c>
       <c r="E32" s="3">
-        <v>25000</v>
+        <v>-40000</v>
       </c>
       <c r="F32" s="3">
-        <v>-23000</v>
+        <v>-66000</v>
       </c>
       <c r="G32" s="3">
-        <v>-165000</v>
+        <v>-234000</v>
       </c>
       <c r="H32" s="3">
-        <v>-39000</v>
+        <v>-138000</v>
       </c>
       <c r="I32" s="3">
         <v>66000</v>

--- a/AAII_Financials/Yearly/PARA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PARA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
   <si>
     <t>PARA</t>
   </si>
@@ -748,7 +748,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>20418000</v>
+        <v>20017000</v>
       </c>
       <c r="E9" s="3">
         <v>19845000</v>
@@ -760,7 +760,7 @@
         <v>14833000</v>
       </c>
       <c r="H9" s="3">
-        <v>16713000</v>
+        <v>16124000</v>
       </c>
       <c r="I9" s="3">
         <v>15399000</v>
@@ -781,7 +781,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9234000</v>
+        <v>9635000</v>
       </c>
       <c r="E10" s="3">
         <v>10309000</v>
@@ -793,7 +793,7 @@
         <v>10452000</v>
       </c>
       <c r="H10" s="3">
-        <v>10285000</v>
+        <v>10874000</v>
       </c>
       <c r="I10" s="3">
         <v>11026000</v>
@@ -895,25 +895,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2146000</v>
+        <v>2262000</v>
       </c>
       <c r="E14" s="3">
-        <v>770000</v>
+        <v>685000</v>
       </c>
       <c r="F14" s="3">
-        <v>271000</v>
+        <v>-2162000</v>
       </c>
       <c r="G14" s="3">
-        <v>997000</v>
+        <v>515000</v>
       </c>
       <c r="H14" s="3">
-        <v>918000</v>
+        <v>744000</v>
       </c>
       <c r="I14" s="3">
-        <v>585000</v>
+        <v>524000</v>
       </c>
       <c r="J14" s="3">
-        <v>711000</v>
+        <v>235000</v>
       </c>
       <c r="K14" s="3">
         <v>249000</v>
@@ -931,16 +931,16 @@
         <v>418000</v>
       </c>
       <c r="E15" s="3">
-        <v>405000</v>
+        <v>378000</v>
       </c>
       <c r="F15" s="3">
         <v>390000</v>
       </c>
       <c r="G15" s="3">
-        <v>405000</v>
+        <v>393000</v>
       </c>
       <c r="H15" s="3">
-        <v>438000</v>
+        <v>418000</v>
       </c>
       <c r="I15" s="3">
         <v>427000</v>
@@ -973,25 +973,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>30227000</v>
+        <v>27797000</v>
       </c>
       <c r="E17" s="3">
-        <v>27997000</v>
+        <v>27321000</v>
       </c>
       <c r="F17" s="3">
-        <v>22460000</v>
+        <v>24585000</v>
       </c>
       <c r="G17" s="3">
-        <v>21341000</v>
+        <v>20620000</v>
       </c>
       <c r="H17" s="3">
-        <v>22951000</v>
+        <v>22122000</v>
       </c>
       <c r="I17" s="3">
-        <v>21345000</v>
+        <v>20939000</v>
       </c>
       <c r="J17" s="3">
-        <v>21232000</v>
+        <v>21178000</v>
       </c>
       <c r="K17" s="3">
         <v>10475000</v>
@@ -1006,25 +1006,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-575000</v>
+        <v>1855000</v>
       </c>
       <c r="E18" s="3">
-        <v>2157000</v>
+        <v>2833000</v>
       </c>
       <c r="F18" s="3">
-        <v>6126000</v>
+        <v>4001000</v>
       </c>
       <c r="G18" s="3">
-        <v>3944000</v>
+        <v>4665000</v>
       </c>
       <c r="H18" s="3">
-        <v>4047000</v>
+        <v>4876000</v>
       </c>
       <c r="I18" s="3">
-        <v>5080000</v>
+        <v>5486000</v>
       </c>
       <c r="J18" s="3">
-        <v>5303000</v>
+        <v>5357000</v>
       </c>
       <c r="K18" s="3">
         <v>2691000</v>
@@ -1054,25 +1054,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>242000</v>
+        <v>423000</v>
       </c>
       <c r="E20" s="3">
-        <v>40000</v>
+        <v>263000</v>
       </c>
       <c r="F20" s="3">
+        <v>115000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>60000</v>
+      </c>
+      <c r="H20" s="3">
         <v>66000</v>
       </c>
-      <c r="G20" s="3">
-        <v>234000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>138000</v>
-      </c>
       <c r="I20" s="3">
-        <v>-66000</v>
+        <v>74000</v>
       </c>
       <c r="J20" s="3">
-        <v>-95000</v>
+        <v>-3000</v>
       </c>
       <c r="K20" s="3">
         <v>-50000</v>
@@ -1087,25 +1087,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>85000</v>
+        <v>1850000</v>
       </c>
       <c r="E21" s="3">
-        <v>2602000</v>
+        <v>2948000</v>
       </c>
       <c r="F21" s="3">
-        <v>6582000</v>
+        <v>4276000</v>
       </c>
       <c r="G21" s="3">
-        <v>4608000</v>
+        <v>4998000</v>
       </c>
       <c r="H21" s="3">
-        <v>4628000</v>
+        <v>5228000</v>
       </c>
       <c r="I21" s="3">
-        <v>5447000</v>
+        <v>5839000</v>
       </c>
       <c r="J21" s="3">
-        <v>5651000</v>
+        <v>5803000</v>
       </c>
       <c r="K21" s="3">
         <v>2866000</v>
@@ -1153,25 +1153,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1253000</v>
+        <v>-1613000</v>
       </c>
       <c r="E23" s="3">
-        <v>1266000</v>
+        <v>1062000</v>
       </c>
       <c r="F23" s="3">
-        <v>5206000</v>
+        <v>5115000</v>
       </c>
       <c r="G23" s="3">
-        <v>3147000</v>
+        <v>3119000</v>
       </c>
       <c r="H23" s="3">
-        <v>3223000</v>
+        <v>3170000</v>
       </c>
       <c r="I23" s="3">
-        <v>3984000</v>
+        <v>3937000</v>
       </c>
       <c r="J23" s="3">
-        <v>4120000</v>
+        <v>4124000</v>
       </c>
       <c r="K23" s="3">
         <v>2230000</v>
@@ -1198,13 +1198,13 @@
         <v>535000</v>
       </c>
       <c r="H24" s="3">
-        <v>15000</v>
+        <v>-29000</v>
       </c>
       <c r="I24" s="3">
-        <v>660000</v>
+        <v>580000</v>
       </c>
       <c r="J24" s="3">
-        <v>796000</v>
+        <v>804000</v>
       </c>
       <c r="K24" s="3">
         <v>628000</v>
@@ -1252,25 +1252,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-892000</v>
+        <v>-1252000</v>
       </c>
       <c r="E26" s="3">
-        <v>1039000</v>
+        <v>835000</v>
       </c>
       <c r="F26" s="3">
-        <v>4560000</v>
+        <v>4469000</v>
       </c>
       <c r="G26" s="3">
-        <v>2612000</v>
+        <v>2584000</v>
       </c>
       <c r="H26" s="3">
-        <v>3208000</v>
+        <v>3199000</v>
       </c>
       <c r="I26" s="3">
-        <v>3324000</v>
+        <v>3357000</v>
       </c>
       <c r="J26" s="3">
-        <v>3324000</v>
+        <v>3320000</v>
       </c>
       <c r="K26" s="3">
         <v>1602000</v>
@@ -1285,25 +1285,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1342000</v>
+        <v>-666000</v>
       </c>
       <c r="E27" s="3">
-        <v>667000</v>
+        <v>1046000</v>
       </c>
       <c r="F27" s="3">
-        <v>4336800</v>
+        <v>4499000</v>
       </c>
       <c r="G27" s="3">
-        <v>2305000</v>
+        <v>2422000</v>
       </c>
       <c r="H27" s="3">
-        <v>3124000</v>
+        <v>3308000</v>
       </c>
       <c r="I27" s="3">
-        <v>3240000</v>
+        <v>3455000</v>
       </c>
       <c r="J27" s="3">
-        <v>3276000</v>
+        <v>2321000</v>
       </c>
       <c r="K27" s="3">
         <v>1552000</v>
@@ -1363,13 +1363,13 @@
         <v>117000</v>
       </c>
       <c r="H29" s="3">
-        <v>184000</v>
+        <v>140000</v>
       </c>
       <c r="I29" s="3">
-        <v>215000</v>
+        <v>135000</v>
       </c>
       <c r="J29" s="3">
-        <v>-955000</v>
+        <v>-947000</v>
       </c>
       <c r="K29" s="3">
         <v>-291000</v>
@@ -1450,25 +1450,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-242000</v>
+        <v>-423000</v>
       </c>
       <c r="E32" s="3">
-        <v>-40000</v>
+        <v>-263000</v>
       </c>
       <c r="F32" s="3">
+        <v>-115000</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-66000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-234000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-138000</v>
-      </c>
       <c r="I32" s="3">
-        <v>66000</v>
+        <v>-74000</v>
       </c>
       <c r="J32" s="3">
-        <v>95000</v>
+        <v>3000</v>
       </c>
       <c r="K32" s="3">
         <v>50000</v>
@@ -1483,13 +1483,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-666000</v>
+        <v>-608000</v>
       </c>
       <c r="E33" s="3">
-        <v>1046000</v>
+        <v>1104000</v>
       </c>
       <c r="F33" s="3">
-        <v>4498800</v>
+        <v>4543000</v>
       </c>
       <c r="G33" s="3">
         <v>2422000</v>
@@ -1549,13 +1549,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-666000</v>
+        <v>-608000</v>
       </c>
       <c r="E35" s="3">
-        <v>1046000</v>
+        <v>1104000</v>
       </c>
       <c r="F35" s="3">
-        <v>4498800</v>
+        <v>4543000</v>
       </c>
       <c r="G35" s="3">
         <v>2422000</v>
@@ -1782,25 +1782,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1714000</v>
+        <v>37000</v>
       </c>
       <c r="E45" s="3">
-        <v>2095000</v>
+        <v>787000</v>
       </c>
       <c r="F45" s="3">
-        <v>1921000</v>
+        <v>745000</v>
       </c>
       <c r="G45" s="3">
-        <v>2021000</v>
+        <v>630000</v>
       </c>
       <c r="H45" s="3">
-        <v>1620000</v>
+        <v>1221000</v>
       </c>
       <c r="I45" s="3">
-        <v>1067000</v>
+        <v>668000</v>
       </c>
       <c r="J45" s="3">
-        <v>463000</v>
+        <v>269000</v>
       </c>
       <c r="K45" s="3">
         <v>724000</v>
@@ -1854,7 +1854,7 @@
         <v>375000</v>
       </c>
       <c r="F47" s="3">
-        <v>627000</v>
+        <v>568000</v>
       </c>
       <c r="G47" s="3">
         <v>601000</v>
@@ -1862,11 +1862,11 @@
       <c r="H47" s="3">
         <v>753000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
+      <c r="I47" s="3">
+        <v>719000</v>
+      </c>
+      <c r="J47" s="3">
+        <v>307000</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -1899,7 +1899,7 @@
         <v>2079000</v>
       </c>
       <c r="J48" s="3">
-        <v>1280000</v>
+        <v>1246000</v>
       </c>
       <c r="K48" s="3">
         <v>1241000</v>
@@ -2013,25 +2013,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>18790000</v>
+        <v>17548000</v>
       </c>
       <c r="E52" s="3">
-        <v>21938000</v>
+        <v>20696000</v>
       </c>
       <c r="F52" s="3">
-        <v>18595000</v>
+        <v>17448000</v>
       </c>
       <c r="G52" s="3">
-        <v>15249000</v>
+        <v>14256000</v>
       </c>
       <c r="H52" s="3">
-        <v>13612000</v>
+        <v>12674000</v>
       </c>
       <c r="I52" s="3">
-        <v>11069000</v>
+        <v>10084000</v>
       </c>
       <c r="J52" s="3">
-        <v>5733000</v>
+        <v>5449000</v>
       </c>
       <c r="K52" s="3">
         <v>9437000</v>
@@ -2175,22 +2175,22 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1000</v>
+        <v>259000</v>
       </c>
       <c r="E58" s="3">
-        <v>239000</v>
+        <v>531000</v>
       </c>
       <c r="F58" s="3">
-        <v>11000</v>
+        <v>336000</v>
       </c>
       <c r="G58" s="3">
-        <v>16000</v>
+        <v>322000</v>
       </c>
       <c r="H58" s="3">
-        <v>717000</v>
+        <v>1006000</v>
       </c>
       <c r="I58" s="3">
-        <v>1687000</v>
+        <v>1013000</v>
       </c>
       <c r="J58" s="3">
         <v>698000</v>
@@ -2208,25 +2208,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>8555000</v>
+        <v>6193000</v>
       </c>
       <c r="E59" s="3">
-        <v>9549000</v>
+        <v>7186000</v>
       </c>
       <c r="F59" s="3">
-        <v>8668000</v>
+        <v>6020000</v>
       </c>
       <c r="G59" s="3">
-        <v>7709000</v>
+        <v>5689000</v>
       </c>
       <c r="H59" s="3">
-        <v>9199000</v>
+        <v>5681000</v>
       </c>
       <c r="I59" s="3">
-        <v>7866000</v>
+        <v>5173000</v>
       </c>
       <c r="J59" s="3">
-        <v>3043000</v>
+        <v>2246000</v>
       </c>
       <c r="K59" s="3">
         <v>3087000</v>
@@ -2274,19 +2274,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14601000</v>
+        <v>15857000</v>
       </c>
       <c r="E61" s="3">
-        <v>15607000</v>
+        <v>17035000</v>
       </c>
       <c r="F61" s="3">
-        <v>17698000</v>
+        <v>19296000</v>
       </c>
       <c r="G61" s="3">
-        <v>19717000</v>
+        <v>21300000</v>
       </c>
       <c r="H61" s="3">
-        <v>18002000</v>
+        <v>19707000</v>
       </c>
       <c r="I61" s="3">
         <v>18100000</v>
@@ -2307,25 +2307,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6228000</v>
+        <v>3086000</v>
       </c>
       <c r="E62" s="3">
-        <v>7789000</v>
+        <v>3939000</v>
       </c>
       <c r="F62" s="3">
-        <v>8153000</v>
+        <v>3650000</v>
       </c>
       <c r="G62" s="3">
-        <v>8177000</v>
+        <v>3796000</v>
       </c>
       <c r="H62" s="3">
-        <v>8729000</v>
+        <v>4430000</v>
       </c>
       <c r="I62" s="3">
-        <v>7334000</v>
+        <v>4668000</v>
       </c>
       <c r="J62" s="3">
-        <v>5387000</v>
+        <v>3621000</v>
       </c>
       <c r="K62" s="3">
         <v>5488000</v>
@@ -2439,22 +2439,22 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>31017000</v>
+        <v>30493000</v>
       </c>
       <c r="E66" s="3">
-        <v>35357000</v>
+        <v>34787000</v>
       </c>
       <c r="F66" s="3">
-        <v>36218000</v>
+        <v>35543000</v>
       </c>
       <c r="G66" s="3">
-        <v>37292000</v>
+        <v>36410000</v>
       </c>
       <c r="H66" s="3">
-        <v>36378000</v>
+        <v>36042000</v>
       </c>
       <c r="I66" s="3">
-        <v>34048000</v>
+        <v>33755000</v>
       </c>
       <c r="J66" s="3">
         <v>18865000</v>
@@ -2855,13 +2855,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-666000</v>
+        <v>-608000</v>
       </c>
       <c r="E81" s="3">
-        <v>1046000</v>
+        <v>1104000</v>
       </c>
       <c r="F81" s="3">
-        <v>4498800</v>
+        <v>4543000</v>
       </c>
       <c r="G81" s="3">
         <v>2422000</v>
@@ -2903,25 +2903,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>418000</v>
+        <v>383000</v>
       </c>
       <c r="E83" s="3">
-        <v>405000</v>
+        <v>337000</v>
       </c>
       <c r="F83" s="3">
-        <v>390000</v>
+        <v>344000</v>
       </c>
       <c r="G83" s="3">
-        <v>430000</v>
+        <v>333000</v>
       </c>
       <c r="H83" s="3">
-        <v>443000</v>
+        <v>362000</v>
       </c>
       <c r="I83" s="3">
-        <v>433000</v>
+        <v>377000</v>
       </c>
       <c r="J83" s="3">
-        <v>443000</v>
+        <v>395000</v>
       </c>
       <c r="K83" s="3">
         <v>225000</v>
@@ -3161,10 +3161,10 @@
         <v>-324000</v>
       </c>
       <c r="H91" s="3">
-        <v>-353000</v>
+        <v>-345000</v>
       </c>
       <c r="I91" s="3">
-        <v>-352000</v>
+        <v>-345000</v>
       </c>
       <c r="J91" s="3">
         <v>-356000</v>
@@ -3296,25 +3296,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-447000</v>
+        <v>389000</v>
       </c>
       <c r="E96" s="3">
-        <v>-689000</v>
+        <v>631000</v>
       </c>
       <c r="F96" s="3">
-        <v>-647000</v>
+        <v>617000</v>
       </c>
       <c r="G96" s="3">
-        <v>-600000</v>
+        <v>600000</v>
       </c>
       <c r="H96" s="3">
-        <v>-595000</v>
+        <v>595000</v>
       </c>
       <c r="I96" s="3">
-        <v>-599000</v>
+        <v>599000</v>
       </c>
       <c r="J96" s="3">
-        <v>-616000</v>
+        <v>616000</v>
       </c>
       <c r="K96" s="3">
         <v>-288000</v>

--- a/AAII_Financials/Yearly/PARA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PARA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>PARA</t>
   </si>
@@ -656,160 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>29213000</v>
+      </c>
+      <c r="E8" s="3">
         <v>29652000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>30154000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28586000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25285000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>26998000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>26425000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>26535000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13166000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12671000</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>19437000</v>
+      </c>
+      <c r="E9" s="3">
         <v>20017000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19845000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17744000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14833000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16124000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15399000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15483000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7956000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7911000</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9776000</v>
+      </c>
+      <c r="E10" s="3">
         <v>9635000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10309000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10842000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10452000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10874000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11026000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11052000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5210000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4760000</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -823,8 +835,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -855,9 +868,12 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,75 +904,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7950000</v>
+      </c>
+      <c r="E14" s="3">
         <v>2262000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>685000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-2162000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>515000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>744000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>524000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>235000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>249000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>390000</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>392000</v>
+      </c>
+      <c r="E15" s="3">
         <v>418000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>378000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>390000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>393000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>418000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>427000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>443000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>225000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>235000</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,74 +992,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>26688000</v>
+      </c>
+      <c r="E17" s="3">
         <v>27797000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27321000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24585000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>20620000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>22122000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20939000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>21178000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10475000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10013000</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2525000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1855000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2833000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4001000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4665000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4876000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5486000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5357000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2691000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2658000</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,173 +1080,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>334000</v>
+      </c>
+      <c r="E20" s="3">
         <v>423000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>263000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>115000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>60000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>66000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>74000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-50000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5000</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2583000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1850000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2948000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4276000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4998000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5228000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5839000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5803000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2866000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2898000</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>860000</v>
+      </c>
+      <c r="E22" s="3">
         <v>920000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>931000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>986000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1031000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>962000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1030000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1088000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>411000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>399000</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6468000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1613000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1062000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5115000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3119000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3170000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3937000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4124000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2230000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2264000</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-305000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-361000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>227000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>646000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>535000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-29000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>580000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>804000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>628000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>676000</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,75 +1293,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6163000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1252000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>835000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4469000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2584000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3199000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3357000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3320000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1602000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1588000</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6204000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-666000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1046000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4499000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2422000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3308000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3455000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2321000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1552000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1554000</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,42 +1401,48 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E29" s="3">
         <v>676000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>379000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>162000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>117000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>140000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>135000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-947000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-291000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-141000</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,75 +1509,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-334000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-423000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-263000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-115000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-60000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-66000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-74000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>50000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5000</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6190000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-608000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1104000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4543000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2422000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3308000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3455000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2321000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1261000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1413000</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,80 +1617,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6190000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-608000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1104000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4543000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2422000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3308000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3455000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2321000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1261000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1413000</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,41 +1729,45 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2661000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2460000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2885000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6267000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2984000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>632000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>856000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>285000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>598000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>323000</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1709,240 +1798,264 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6920000</v>
+      </c>
+      <c r="E43" s="3">
         <v>7115000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7412000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6984000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7017000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6837000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7199000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3697000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3314000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3628000</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1429000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1414000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1342000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1504000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1757000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2813000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2785000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1828000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1427000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1271000</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>37000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>787000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>745000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>630000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1221000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>668000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>269000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>724000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>525000</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12542000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12703000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13734000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16676000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13779000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11902000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11880000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6273000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6063000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5747000</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>96000</v>
+        <v>185000</v>
       </c>
       <c r="E47" s="3">
+        <v>708000</v>
+      </c>
+      <c r="F47" s="3">
         <v>375000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>568000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>601000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>753000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>719000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>307000</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2578000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2849000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3153000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3366000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3596000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3783000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2079000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1246000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1241000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1405000</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12914000</v>
+      </c>
+      <c r="E49" s="3">
         <v>19105000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19193000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19356000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19438000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19535000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19469000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7557000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7497000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11995000</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,42 +2122,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>17548000</v>
+        <v>16567000</v>
       </c>
       <c r="E52" s="3">
+        <v>16936000</v>
+      </c>
+      <c r="F52" s="3">
         <v>20696000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17448000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14256000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12674000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10084000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5449000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9437000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4618000</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,42 +2194,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>46172000</v>
+      </c>
+      <c r="E54" s="3">
         <v>53543000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>58393000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>58620000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>52663000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>49585000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44497000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>20843000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24238000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23765000</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,206 +2265,225 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>953000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1403000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>800000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>571000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>632000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>502000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>231000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>148000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>192000</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>284000</v>
+      </c>
+      <c r="E58" s="3">
         <v>259000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>531000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>336000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>322000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1006000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1013000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>698000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>473000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>222000</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6195000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6193000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7186000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6020000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5689000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5681000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5173000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2246000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3087000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3146000</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9631000</v>
+      </c>
+      <c r="E60" s="3">
         <v>9656000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11191000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9479000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8296000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9048000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8321000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3972000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3708000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3560000</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15549000</v>
+      </c>
+      <c r="E61" s="3">
         <v>15857000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>17035000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19296000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>21300000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19707000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18100000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9464000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8902000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8226000</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2875000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3086000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3939000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3650000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3796000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4430000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4668000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3621000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5488000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6344000</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,42 +2586,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>29390000</v>
+      </c>
+      <c r="E66" s="3">
         <v>30493000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>34787000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>35543000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36410000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>36042000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33755000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>18865000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20549000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18202000</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,42 +2782,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7487000</v>
+      </c>
+      <c r="E72" s="3">
         <v>13829000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>14737000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14343000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10375000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8494000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5569000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-18900000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-19257000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-20518000</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,42 +2926,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16320000</v>
+      </c>
+      <c r="E76" s="3">
         <v>22526000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23036000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22402000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15371000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13207000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10449000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1978000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3689000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5563000</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,80 +2998,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6190000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-608000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1104000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4543000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2422000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3308000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3455000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2321000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1261000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1413000</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,41 +3094,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E83" s="3">
         <v>383000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>337000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>344000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>333000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>362000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>377000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>395000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>225000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>235000</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,42 +3307,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>752000</v>
+      </c>
+      <c r="E89" s="3">
         <v>475000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>219000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>953000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2294000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1230000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3464000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2439000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1685000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1394000</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,41 +3362,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-263000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-328000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-358000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-354000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-324000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-345000</v>
       </c>
       <c r="I91" s="3">
         <v>-345000</v>
       </c>
       <c r="J91" s="3">
+        <v>-345000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-356000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-196000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-171000</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,42 +3467,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E94" s="3">
         <v>942000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-526000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2395000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>56000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-155000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-611000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>126000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-340000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>154000</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,41 +3522,45 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E96" s="3">
         <v>389000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>631000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>617000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>600000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>595000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>599000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>616000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-288000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-300000</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,106 +3663,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-507000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1841000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2981000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-152000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-90000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1216000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2531000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3009000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1046000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1653000</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-94000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-48000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>25000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-25000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>58000</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>201000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-425000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3382000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3148000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2285000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-142000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>297000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-386000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>299000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-105000</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
